--- a/shift.xlsx
+++ b/shift.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="32">
   <si>
     <t>Ime</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>11 16</t>
+  </si>
+  <si>
+    <t>10 8</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
         <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s">
         <v>16</v>
